--- a/Scandic modell.xlsx
+++ b/Scandic modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC30F1BB-0E32-9746-8AE8-148322C3281E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854C8700-263B-044F-9D4F-BBD13645898F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17200" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="25080" yWindow="500" windowWidth="26120" windowHeight="26740" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -650,7 +650,7 @@
     <numFmt numFmtId="166" formatCode="0.0\ %"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -734,12 +734,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -818,7 +812,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -888,6 +882,11 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2855,7 +2854,7 @@
     <col min="15" max="28" width="10.33203125" style="2" customWidth="1"/>
     <col min="29" max="35" width="10.83203125" style="2"/>
     <col min="36" max="36" width="11" style="2" customWidth="1"/>
-    <col min="37" max="37" width="11.5" style="2" customWidth="1"/>
+    <col min="37" max="37" width="11.5" style="4" customWidth="1"/>
     <col min="38" max="38" width="10.83203125" style="2"/>
     <col min="39" max="39" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="12.1640625" style="2" customWidth="1"/>
@@ -2995,7 +2994,7 @@
       <c r="AJ3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AK3" s="59" t="s">
         <v>19</v>
       </c>
       <c r="AL3" s="7" t="s">
@@ -3031,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>41</v>
@@ -3119,7 +3118,7 @@
       <c r="AJ4" s="13">
         <v>22288</v>
       </c>
-      <c r="AK4" s="13">
+      <c r="AK4" s="14">
         <f>AJ4*1.04</f>
         <v>23179.52</v>
       </c>
@@ -3252,7 +3251,7 @@
       <c r="AJ5" s="13">
         <v>0</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AK5" s="14">
         <v>0</v>
       </c>
       <c r="AL5" s="13">
@@ -3289,7 +3288,7 @@
       </c>
       <c r="B6" s="5">
         <f>B4*B5</f>
-        <v>17326.921920000001</v>
+        <v>18951.32085</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>43</v>
@@ -3410,7 +3409,7 @@
         <f>SUM(AJ4:AJ5)</f>
         <v>22288</v>
       </c>
-      <c r="AK6" s="12">
+      <c r="AK6" s="56">
         <f t="shared" ref="AK6:AT6" si="4">SUM(AK4:AK5)</f>
         <v>23179.52</v>
       </c>
@@ -3544,7 +3543,7 @@
       <c r="AJ7" s="13">
         <v>-1637</v>
       </c>
-      <c r="AK7" s="13">
+      <c r="AK7" s="14">
         <f>AJ7*1.02</f>
         <v>-1669.74</v>
       </c>
@@ -3678,7 +3677,7 @@
       <c r="AJ8" s="13">
         <v>-4614</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AK8" s="14">
         <f t="shared" ref="AK8:AK13" si="6">AJ8*1.02</f>
         <v>-4706.28</v>
       </c>
@@ -3725,7 +3724,7 @@
       </c>
       <c r="B9" s="6">
         <f>B6-B7+B8</f>
-        <v>17597.921920000001</v>
+        <v>19222.32085</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>46</v>
@@ -3812,7 +3811,7 @@
       <c r="AJ9" s="13">
         <v>-7025</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AK9" s="14">
         <f t="shared" si="6"/>
         <v>-7165.5</v>
       </c>
@@ -3946,7 +3945,7 @@
       <c r="AJ10" s="13">
         <v>-2230</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AK10" s="14">
         <f t="shared" si="6"/>
         <v>-2274.6</v>
       </c>
@@ -4077,7 +4076,7 @@
       <c r="AJ11" s="13">
         <v>-75</v>
       </c>
-      <c r="AK11" s="13">
+      <c r="AK11" s="14">
         <f t="shared" si="6"/>
         <v>-76.5</v>
       </c>
@@ -4212,7 +4211,7 @@
       <c r="AJ12" s="13">
         <v>-51</v>
       </c>
-      <c r="AK12" s="13">
+      <c r="AK12" s="14">
         <f t="shared" si="6"/>
         <v>-52.02</v>
       </c>
@@ -4339,7 +4338,7 @@
       <c r="AJ13" s="13">
         <v>-3996</v>
       </c>
-      <c r="AK13" s="13">
+      <c r="AK13" s="14">
         <f t="shared" si="6"/>
         <v>-4075.92</v>
       </c>
@@ -4504,7 +4503,7 @@
         <f t="shared" ref="AJ14:AT14" si="12">SUM(AJ7:AJ13)</f>
         <v>-19628</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AK14" s="14">
         <f t="shared" si="12"/>
         <v>-20020.560000000001</v>
       </c>
@@ -4665,7 +4664,7 @@
         <f>SUM(AJ6:AJ13)</f>
         <v>2660</v>
       </c>
-      <c r="AK15" s="12">
+      <c r="AK15" s="56">
         <f t="shared" ref="AK15:AT15" si="15">SUM(AK6:AK13)</f>
         <v>3158.9599999999991</v>
       </c>
@@ -4792,7 +4791,7 @@
       <c r="AJ16" s="13">
         <v>-1853</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AK16" s="14">
         <f>AJ16*1.01</f>
         <v>-1871.53</v>
       </c>
@@ -4953,7 +4952,7 @@
         <f t="shared" ref="AJ17:AT17" si="20">SUM(AJ15:AJ16)</f>
         <v>807</v>
       </c>
-      <c r="AK17" s="13">
+      <c r="AK17" s="14">
         <f t="shared" si="20"/>
         <v>1287.4299999999992</v>
       </c>
@@ -5089,7 +5088,7 @@
       <c r="AJ18" s="13">
         <v>-185</v>
       </c>
-      <c r="AK18" s="13">
+      <c r="AK18" s="14">
         <f>AK17*-0.2</f>
         <v>-257.48599999999982</v>
       </c>
@@ -5250,7 +5249,7 @@
         <f t="shared" ref="AJ19:AT19" si="25">SUM(AJ17:AJ18)</f>
         <v>622</v>
       </c>
-      <c r="AK19" s="12">
+      <c r="AK19" s="56">
         <f t="shared" si="25"/>
         <v>1029.9439999999993</v>
       </c>
@@ -5820,7 +5819,7 @@
       <c r="AJ20" s="9">
         <v>215.12729999999999</v>
       </c>
-      <c r="AK20" s="9">
+      <c r="AK20" s="8">
         <v>215.12729999999999</v>
       </c>
       <c r="AL20" s="9">
@@ -5973,7 +5972,7 @@
         <f t="shared" ref="AJ21:AT21" si="33">AJ19/AJ20</f>
         <v>2.8913113305470763</v>
       </c>
-      <c r="AK21" s="16">
+      <c r="AK21" s="60">
         <f t="shared" si="33"/>
         <v>4.7876025032620193</v>
       </c>
@@ -6130,7 +6129,7 @@
         <f t="shared" si="41"/>
         <v>1.4982467325470195E-2</v>
       </c>
-      <c r="AK23" s="20">
+      <c r="AK23" s="19">
         <f t="shared" si="41"/>
         <v>4.0000000000000022E-2</v>
       </c>
@@ -6222,6 +6221,7 @@
       <c r="AJ24" s="20">
         <v>0.04</v>
       </c>
+      <c r="AK24" s="19"/>
       <c r="AV24" s="21" t="s">
         <v>2</v>
       </c>
@@ -6334,7 +6334,7 @@
         <f t="shared" si="45"/>
         <v>2.6407990378078755E-2</v>
       </c>
-      <c r="AK25" s="20">
+      <c r="AK25" s="19">
         <f t="shared" si="45"/>
         <v>2.0000000000000066E-2</v>
       </c>
@@ -6502,7 +6502,7 @@
         <f>AJ15/AJ6</f>
         <v>0.11934673366834171</v>
       </c>
-      <c r="AK26" s="21">
+      <c r="AK26" s="61">
         <f t="shared" si="48"/>
         <v>0.13628237340548893</v>
       </c>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AW26" s="20">
         <f>(AW25-B4)/B4</f>
-        <v>0.54240861588584666</v>
+        <v>0.41020216309563123</v>
       </c>
     </row>
     <row r="27" spans="2:155" x14ac:dyDescent="0.25">
@@ -6612,7 +6612,7 @@
         <f>AJ19/AJ53</f>
         <v>0.2095687331536388</v>
       </c>
-      <c r="AK27" s="21"/>
+      <c r="AK27" s="61"/>
       <c r="AL27" s="21"/>
       <c r="AM27" s="21"/>
       <c r="AN27" s="21"/>
@@ -6651,7 +6651,7 @@
       <c r="AH28" s="21"/>
       <c r="AI28" s="21"/>
       <c r="AJ28" s="21"/>
-      <c r="AK28" s="21"/>
+      <c r="AK28" s="61"/>
       <c r="AL28" s="21"/>
       <c r="AM28" s="21"/>
       <c r="AN28" s="21"/>
@@ -6756,6 +6756,7 @@
       <c r="AJ29" s="13">
         <v>2425</v>
       </c>
+      <c r="AK29" s="14"/>
       <c r="AV29" s="12"/>
       <c r="AW29" s="12"/>
     </row>
@@ -6880,6 +6881,7 @@
         <f t="shared" si="50"/>
         <v>0.10880294328786791</v>
       </c>
+      <c r="AK30" s="51"/>
       <c r="AV30" s="49"/>
       <c r="AW30" s="49"/>
     </row>
@@ -6948,6 +6950,7 @@
         <f>SUM(R29:U29)</f>
         <v>2502</v>
       </c>
+      <c r="AK31" s="14"/>
       <c r="AV31" s="12"/>
       <c r="AW31" s="12"/>
     </row>
@@ -6973,7 +6976,7 @@
       <c r="AH32" s="21"/>
       <c r="AI32" s="21"/>
       <c r="AJ32" s="21"/>
-      <c r="AK32" s="21"/>
+      <c r="AK32" s="61"/>
       <c r="AL32" s="21"/>
       <c r="AM32" s="21"/>
       <c r="AN32" s="21"/>
@@ -7076,6 +7079,7 @@
       <c r="AJ33" s="12">
         <v>816</v>
       </c>
+      <c r="AK33" s="56"/>
     </row>
     <row r="34" spans="1:46" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="53"/>
@@ -7178,6 +7182,7 @@
         <f>(AJ33-AI33)/AI33</f>
         <v>2.1276595744680851E-2</v>
       </c>
+      <c r="AK34" s="53"/>
     </row>
     <row r="35" spans="1:46" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="14"/>
@@ -7271,6 +7276,7 @@
       <c r="AJ35" s="13">
         <v>1274</v>
       </c>
+      <c r="AK35" s="14"/>
     </row>
     <row r="36" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="51"/>
@@ -7377,6 +7383,7 @@
         <f>(AJ35-AI35)/AI35</f>
         <v>-1.5455950540958269E-2</v>
       </c>
+      <c r="AK36" s="51"/>
     </row>
     <row r="37" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="51"/>
@@ -7470,6 +7477,7 @@
       <c r="AJ37" s="10">
         <v>0.64100000000000001</v>
       </c>
+      <c r="AK37" s="51"/>
     </row>
     <row r="38" spans="1:46" x14ac:dyDescent="0.25">
       <c r="AD38" s="21"/>
@@ -7479,7 +7487,7 @@
       <c r="AH38" s="21"/>
       <c r="AI38" s="21"/>
       <c r="AJ38" s="21"/>
-      <c r="AK38" s="21"/>
+      <c r="AK38" s="61"/>
       <c r="AL38" s="21"/>
       <c r="AM38" s="21"/>
       <c r="AO38" s="21"/>
@@ -7582,6 +7590,7 @@
       <c r="AJ39" s="13">
         <v>68592</v>
       </c>
+      <c r="AK39" s="14"/>
       <c r="AN39" s="21"/>
     </row>
     <row r="40" spans="1:46" x14ac:dyDescent="0.25">
@@ -7810,6 +7819,7 @@
       <c r="AJ43" s="13">
         <v>6825</v>
       </c>
+      <c r="AK43" s="14"/>
     </row>
     <row r="44" spans="1:46" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
@@ -7904,6 +7914,7 @@
       <c r="AJ44" s="13">
         <v>65</v>
       </c>
+      <c r="AK44" s="14"/>
     </row>
     <row r="45" spans="1:46" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
@@ -7998,6 +8009,7 @@
       <c r="AJ45" s="13">
         <v>38659</v>
       </c>
+      <c r="AK45" s="14"/>
     </row>
     <row r="46" spans="1:46" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
@@ -8092,6 +8104,7 @@
       <c r="AJ46" s="13">
         <v>4237</v>
       </c>
+      <c r="AK46" s="14"/>
     </row>
     <row r="47" spans="1:46" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
@@ -8194,6 +8207,7 @@
       <c r="AJ47" s="13">
         <v>689</v>
       </c>
+      <c r="AK47" s="14"/>
     </row>
     <row r="48" spans="1:46" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
@@ -8299,8 +8313,9 @@
       <c r="AJ48" s="13">
         <v>1107</v>
       </c>
-    </row>
-    <row r="49" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK48" s="14"/>
+    </row>
+    <row r="49" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="4"/>
       <c r="C49" s="2" t="s">
@@ -8396,8 +8411,9 @@
       <c r="AJ49" s="13">
         <v>950</v>
       </c>
-    </row>
-    <row r="50" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK49" s="14"/>
+    </row>
+    <row r="50" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="4"/>
       <c r="C50" s="1" t="s">
@@ -8519,8 +8535,9 @@
         <f>SUM(AJ43:AJ49)</f>
         <v>52532</v>
       </c>
-    </row>
-    <row r="51" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK50" s="14"/>
+    </row>
+    <row r="51" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="4"/>
       <c r="C51" s="2" t="s">
@@ -8613,8 +8630,9 @@
       <c r="AJ51" s="13">
         <v>2896</v>
       </c>
-    </row>
-    <row r="52" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK51" s="14"/>
+    </row>
+    <row r="52" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="4"/>
       <c r="C52" s="2" t="s">
@@ -8707,8 +8725,9 @@
       <c r="AJ52" s="13">
         <v>72</v>
       </c>
-    </row>
-    <row r="53" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK52" s="14"/>
+    </row>
+    <row r="53" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="4"/>
       <c r="C53" s="11" t="s">
@@ -8830,8 +8849,9 @@
         <f>SUM(AJ51:AJ52)</f>
         <v>2968</v>
       </c>
-    </row>
-    <row r="54" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK53" s="14"/>
+    </row>
+    <row r="54" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="4"/>
       <c r="C54" s="2" t="s">
@@ -8928,8 +8948,9 @@
       <c r="AJ54" s="13">
         <v>985</v>
       </c>
-    </row>
-    <row r="55" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK54" s="14"/>
+    </row>
+    <row r="55" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="4"/>
       <c r="C55" s="2" t="s">
@@ -9022,8 +9043,9 @@
       <c r="AJ55" s="13">
         <v>41024</v>
       </c>
-    </row>
-    <row r="56" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK55" s="14"/>
+    </row>
+    <row r="56" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="4"/>
       <c r="C56" s="2" t="s">
@@ -9124,8 +9146,9 @@
       <c r="AJ56" s="13">
         <v>1053</v>
       </c>
-    </row>
-    <row r="57" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK56" s="14"/>
+    </row>
+    <row r="57" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="4"/>
       <c r="C57" s="2" t="s">
@@ -9221,8 +9244,9 @@
       <c r="AJ57" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK57" s="14"/>
+    </row>
+    <row r="58" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="4"/>
       <c r="C58" s="2" t="s">
@@ -9315,8 +9339,9 @@
       <c r="AJ58" s="13">
         <v>2668</v>
       </c>
-    </row>
-    <row r="59" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK58" s="14"/>
+    </row>
+    <row r="59" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="4"/>
       <c r="C59" s="2" t="s">
@@ -9413,8 +9438,9 @@
       <c r="AJ59" s="13">
         <v>14</v>
       </c>
-    </row>
-    <row r="60" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK59" s="14"/>
+    </row>
+    <row r="60" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="4"/>
       <c r="C60" s="2" t="s">
@@ -9515,8 +9541,9 @@
       <c r="AJ60" s="13">
         <v>3820</v>
       </c>
-    </row>
-    <row r="61" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK60" s="14"/>
+    </row>
+    <row r="61" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="4"/>
       <c r="C61" s="11" t="s">
@@ -9638,8 +9665,9 @@
         <f>SUM(AJ54:AJ60)</f>
         <v>49564</v>
       </c>
-    </row>
-    <row r="62" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK61" s="14"/>
+    </row>
+    <row r="62" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="4"/>
       <c r="C62" s="1" t="s">
@@ -9761,8 +9789,9 @@
         <f>AJ53+AJ61</f>
         <v>52532</v>
       </c>
-    </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK62" s="14"/>
+    </row>
+    <row r="63" spans="1:37" x14ac:dyDescent="0.25">
       <c r="D63" s="13"/>
       <c r="E63" s="13"/>
       <c r="F63" s="13"/>
@@ -9775,7 +9804,7 @@
       <c r="M63" s="13"/>
       <c r="N63" s="13"/>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C64" s="3" t="s">
         <v>61</v>
       </c>
@@ -9806,7 +9835,7 @@
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
     </row>
-    <row r="65" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="4"/>
       <c r="C65" s="2" t="s">
@@ -9931,8 +9960,9 @@
         <f t="shared" si="85"/>
         <v>2660</v>
       </c>
-    </row>
-    <row r="66" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK65" s="14"/>
+    </row>
+    <row r="66" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="4"/>
       <c r="C66" s="2" t="s">
@@ -10028,8 +10058,9 @@
       <c r="AJ66" s="13">
         <v>2661</v>
       </c>
-    </row>
-    <row r="67" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK66" s="14"/>
+    </row>
+    <row r="67" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="4"/>
       <c r="C67" s="2" t="s">
@@ -10125,8 +10156,9 @@
       <c r="AJ67" s="13">
         <v>1090</v>
       </c>
-    </row>
-    <row r="68" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK67" s="14"/>
+    </row>
+    <row r="68" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="4"/>
       <c r="C68" s="2" t="s">
@@ -10235,8 +10267,9 @@
       <c r="AJ68" s="13">
         <v>2973</v>
       </c>
-    </row>
-    <row r="69" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK68" s="14"/>
+    </row>
+    <row r="69" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="4"/>
       <c r="C69" s="2" t="s">
@@ -10332,8 +10365,9 @@
       <c r="AJ69" s="13">
         <v>-301</v>
       </c>
-    </row>
-    <row r="70" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK69" s="14"/>
+    </row>
+    <row r="70" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="4"/>
       <c r="C70" s="2" t="s">
@@ -10439,8 +10473,9 @@
       <c r="AJ70" s="13">
         <v>37</v>
       </c>
-    </row>
-    <row r="71" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK70" s="14"/>
+    </row>
+    <row r="71" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="4"/>
       <c r="C71" s="1" t="s">
@@ -10565,8 +10600,9 @@
         <f t="shared" si="93"/>
         <v>6460</v>
       </c>
-    </row>
-    <row r="72" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK71" s="14"/>
+    </row>
+    <row r="72" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="4"/>
       <c r="C72" s="2"/>
@@ -10576,8 +10612,9 @@
       <c r="V72" s="2"/>
       <c r="X72" s="2"/>
       <c r="Y72" s="2"/>
-    </row>
-    <row r="73" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK72" s="14"/>
+    </row>
+    <row r="73" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="4"/>
       <c r="C73" s="2" t="s">
@@ -10677,8 +10714,9 @@
       <c r="AJ73" s="13">
         <v>-1123</v>
       </c>
-    </row>
-    <row r="74" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK73" s="14"/>
+    </row>
+    <row r="74" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="4"/>
       <c r="C74" s="1" t="s">
@@ -10803,8 +10841,9 @@
         <f>SUM(AJ73)</f>
         <v>-1123</v>
       </c>
-    </row>
-    <row r="75" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK74" s="14"/>
+    </row>
+    <row r="75" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="4"/>
       <c r="C75" s="2"/>
@@ -10814,8 +10853,9 @@
       <c r="V75" s="2"/>
       <c r="X75" s="2"/>
       <c r="Y75" s="2"/>
-    </row>
-    <row r="76" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK75" s="14"/>
+    </row>
+    <row r="76" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="4"/>
       <c r="C76" s="2" t="s">
@@ -10912,8 +10952,9 @@
       <c r="AJ76" s="13">
         <v>-361</v>
       </c>
-    </row>
-    <row r="77" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK76" s="14"/>
+    </row>
+    <row r="77" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="4"/>
       <c r="C77" s="2" t="s">
@@ -11007,8 +11048,9 @@
       <c r="AJ77" s="13">
         <v>-436</v>
       </c>
-    </row>
-    <row r="78" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK77" s="14"/>
+    </row>
+    <row r="78" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="4"/>
       <c r="C78" s="2" t="s">
@@ -11110,8 +11152,9 @@
       <c r="AJ78" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK78" s="14"/>
+    </row>
+    <row r="79" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="4"/>
       <c r="C79" s="2" t="s">
@@ -11207,8 +11250,9 @@
       <c r="AJ79" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK79" s="14"/>
+    </row>
+    <row r="80" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="4"/>
       <c r="C80" s="2" t="s">
@@ -11304,8 +11348,9 @@
       <c r="AJ80" s="13">
         <v>-248</v>
       </c>
-    </row>
-    <row r="81" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK80" s="14"/>
+    </row>
+    <row r="81" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="4"/>
       <c r="C81" s="2" t="s">
@@ -11401,8 +11446,9 @@
       <c r="AJ81" s="13">
         <v>-283</v>
       </c>
-    </row>
-    <row r="82" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK81" s="14"/>
+    </row>
+    <row r="82" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="4"/>
       <c r="C82" s="2" t="s">
@@ -11499,8 +11545,9 @@
       <c r="AJ82" s="13">
         <v>-2618</v>
       </c>
-    </row>
-    <row r="83" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK82" s="14"/>
+    </row>
+    <row r="83" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="4"/>
       <c r="C83" s="2" t="s">
@@ -11597,8 +11644,9 @@
       <c r="AJ83" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK83" s="14"/>
+    </row>
+    <row r="84" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="4"/>
       <c r="C84" s="2" t="s">
@@ -11694,8 +11742,9 @@
       <c r="AJ84" s="13">
         <v>-889</v>
       </c>
-    </row>
-    <row r="85" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK84" s="14"/>
+    </row>
+    <row r="85" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="4"/>
       <c r="C85" s="2" t="s">
@@ -11793,8 +11842,9 @@
       <c r="AJ85" s="13">
         <v>-452</v>
       </c>
-    </row>
-    <row r="86" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK85" s="14"/>
+    </row>
+    <row r="86" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="4"/>
       <c r="C86" s="1" t="s">
@@ -11919,8 +11969,9 @@
         <f t="shared" si="101"/>
         <v>-5285</v>
       </c>
-    </row>
-    <row r="87" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK86" s="14"/>
+    </row>
+    <row r="87" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="4"/>
       <c r="C87" s="2"/>
@@ -11930,8 +11981,9 @@
       <c r="V87" s="2"/>
       <c r="X87" s="2"/>
       <c r="Y87" s="2"/>
-    </row>
-    <row r="88" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK87" s="14"/>
+    </row>
+    <row r="88" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="4"/>
       <c r="C88" s="2" t="s">
@@ -12056,16 +12108,18 @@
         <f t="shared" ref="AJ88" si="106">AJ71+AJ74+AJ86</f>
         <v>52</v>
       </c>
-    </row>
-    <row r="89" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK88" s="14"/>
+    </row>
+    <row r="89" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="4"/>
       <c r="C89" s="2"/>
       <c r="V89" s="2"/>
       <c r="X89" s="2"/>
       <c r="Y89" s="2"/>
-    </row>
-    <row r="90" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AK89" s="14"/>
+    </row>
+    <row r="90" spans="1:37" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="4"/>
       <c r="C90" s="2" t="s">
@@ -12190,6 +12244,7 @@
         <f>AJ71+AJ73+AJ82</f>
         <v>2719</v>
       </c>
+      <c r="AK90" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -17388,15 +17443,15 @@
       </c>
       <c r="D5" s="33">
         <f>Modell!$B$9/Modell!AK15</f>
-        <v>5.5707960594626096</v>
+        <v>6.0850155905741143</v>
       </c>
       <c r="E5" s="33">
         <f>Modell!$B$9/Modell!AL15</f>
-        <v>3.9295741446361188</v>
+        <v>4.2922985654467425</v>
       </c>
       <c r="F5" s="33">
         <f>Modell!$B$9/Modell!AM15</f>
-        <v>3.7247148290389727</v>
+        <v>4.0685294459210803</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -17405,15 +17460,15 @@
       </c>
       <c r="D6" s="33">
         <f>Modell!$B$4/Modell!AK21</f>
-        <v>16.709825000194193</v>
+        <v>18.2763710939624</v>
       </c>
       <c r="E6" s="33">
         <f>Modell!$B$4/Modell!AL21</f>
-        <v>9.636195784800103</v>
+        <v>10.539589139625113</v>
       </c>
       <c r="F6" s="33">
         <f>Modell!$B$4/Modell!AM21</f>
-        <v>9.090494440872904</v>
+        <v>9.9427282947047395</v>
       </c>
     </row>
   </sheetData>
@@ -17641,7 +17696,7 @@
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <f>AA26</f>
-        <v>-0.56967718164863934</v>
+        <v>-0.60656199465018457</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>43</v>
@@ -19649,7 +19704,7 @@
       </c>
       <c r="AA26" s="20">
         <f>(AA25-Modell!B4)/Modell!B4</f>
-        <v>-0.56967718164863934</v>
+        <v>-0.60656199465018457</v>
       </c>
     </row>
   </sheetData>
